--- a/docs/course_schedule.xlsx
+++ b/docs/course_schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinchen/Library/CloudStorage/Dropbox/NTNU/Programming_Linguistics/NTNU_ENC2055/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EED02B-0D7D-D74C-8933-D9C639C7DEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0FFBFB-9C5C-694E-B206-CCA10A3D71AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="38400" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Week</t>
   </si>
@@ -79,27 +79,9 @@
     <t>Week 16</t>
   </si>
   <si>
-    <t>Midterm Exam</t>
-  </si>
-  <si>
-    <t>Final Exam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science and R </t>
-  </si>
-  <si>
-    <t>R Fundamentals</t>
-  </si>
-  <si>
     <t>Code Format Convention, Subsetting</t>
   </si>
   <si>
-    <t>Conditions and Loops</t>
-  </si>
-  <si>
-    <t>Functions</t>
-  </si>
-  <si>
     <t>Data Visualization</t>
   </si>
   <si>
@@ -122,6 +104,70 @@
   </si>
   <si>
     <t>String Manipulation</t>
+  </si>
+  <si>
+    <t>Holiday</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Holiday</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Holiday</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Conditions, Loops, Functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midterm Exam </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Exam </t>
+  </si>
+  <si>
+    <t>Data Science and R Fundamentals</t>
   </si>
 </sst>
 </file>
@@ -1000,10 +1046,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>45541</v>
+        <v>46276</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1011,10 +1057,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45548</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1022,10 +1068,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>45555</v>
+        <v>46290</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1033,10 +1079,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>45562</v>
+        <v>46297</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1044,10 +1090,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="2">
-        <v>45569</v>
+        <v>46304</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1055,10 +1101,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="2">
-        <v>45576</v>
+        <v>46311</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1066,10 +1112,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>45583</v>
+        <v>46318</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1077,10 +1123,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="5">
-        <v>45590</v>
+        <v>46325</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1088,10 +1134,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>45597</v>
+        <v>46332</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1099,10 +1145,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="2">
-        <v>45604</v>
+        <v>46339</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1110,10 +1156,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>45611</v>
+        <v>46346</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1121,10 +1167,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>45618</v>
+        <v>46353</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1132,10 +1178,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>45625</v>
+        <v>46360</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1143,10 +1189,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>45632</v>
+        <v>46367</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1154,10 +1200,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="2">
-        <v>45639</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>46374</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1165,10 +1211,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="2">
-        <v>45646</v>
+        <v>46381</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/course_schedule.xlsx
+++ b/docs/course_schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinchen/Library/CloudStorage/Dropbox/NTNU/Programming_Linguistics/NTNU_ENC2055/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0FFBFB-9C5C-694E-B206-CCA10A3D71AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A818FF1-708F-094D-8759-53594FD46FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="38400" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="620" windowWidth="38400" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="2" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>Week 16</t>
   </si>
   <si>
-    <t>Code Format Convention, Subsetting</t>
-  </si>
-  <si>
     <t>Data Visualization</t>
   </si>
   <si>
@@ -95,12 +92,6 @@
   </si>
   <si>
     <t>Regular Expressions</t>
-  </si>
-  <si>
-    <t>University Sports Day (No Meeting)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Regular Expressions</t>
   </si>
   <si>
     <t>String Manipulation</t>
@@ -168,6 +159,15 @@
   </si>
   <si>
     <t>Data Science and R Fundamentals</t>
+  </si>
+  <si>
+    <t>Code Format Convention, Subsetting (Guest Lecture)</t>
+  </si>
+  <si>
+    <t>Regular Expressions **</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> University Sports Day (No Meeting) **</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1049,7 @@
         <v>46276</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1060,7 +1060,7 @@
         <v>46283</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1071,7 +1071,7 @@
         <v>46290</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1082,7 +1082,7 @@
         <v>46297</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1093,7 +1093,7 @@
         <v>46304</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1104,7 +1104,7 @@
         <v>46311</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1115,7 +1115,7 @@
         <v>46318</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1126,7 +1126,7 @@
         <v>46325</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1137,7 +1137,7 @@
         <v>46332</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1148,7 +1148,7 @@
         <v>46339</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1158,8 +1158,8 @@
       <c r="B12" s="2">
         <v>46346</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1170,7 +1170,7 @@
         <v>46353</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1181,7 +1181,7 @@
         <v>46360</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1192,7 +1192,7 @@
         <v>46367</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1203,7 +1203,7 @@
         <v>46374</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1214,7 +1214,7 @@
         <v>46381</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
